--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487071_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487071_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. MUZQUIZ GURREA</t>
+          <t>S. HANSEN GUTIERREZ</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.4018</v>
+        <v>-0.0625</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0391</v>
+        <v>-0.0011</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3627</v>
+        <v>-0.0614</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.0908</v>
+        <v>-2.4882</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.718</v>
+        <v>-0.8973</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.3727</v>
+        <v>-1.5908</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.482</v>
+        <v>-0.659</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.5227000000000001</v>
+        <v>0.6519</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0407</v>
+        <v>-1.3109</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.6087</v>
+        <v>-1.8292</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.1953</v>
+        <v>-1.5493</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4134</v>
+        <v>-0.2799</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5441</v>
+        <v>1.9301</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.193</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7371</v>
+        <v>2.1231</v>
       </c>
       <c r="S2" t="n">
-        <v>0.7588</v>
+        <v>-0.7324000000000001</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6359</v>
+        <v>-0.3771</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1229</v>
+        <v>-0.3553</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.614</v>
+        <v>1.228</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.228</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.614</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. HANSEN GUTIERREZ</t>
+          <t>D. MUZQUIZ GURREA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.7506</v>
+        <v>-0.8093</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5018</v>
+        <v>-0.3395</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2487</v>
+        <v>-0.4698</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.4882</v>
+        <v>-2.0908</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8973</v>
+        <v>-1.718</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.5908</v>
+        <v>-0.3727</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.659</v>
+        <v>-0.482</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6519</v>
+        <v>-0.5227000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3109</v>
+        <v>0.0407</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.8292</v>
+        <v>-1.6087</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5493</v>
+        <v>-1.1953</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.2799</v>
+        <v>-0.4134</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.193</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1231</v>
+        <v>1.7371</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4204</v>
+        <v>0.3513</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8778</v>
+        <v>0.3355</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.5427</v>
+        <v>0.0159</v>
       </c>
       <c r="V3" t="n">
-        <v>1.228</v>
+        <v>-0.614</v>
       </c>
       <c r="W3" t="n">
-        <v>1.228</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.614</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. SAEZ PEREZ</t>
+          <t>J. LAMBAS VIVANCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-2.0345</v>
+        <v>-2.0416</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4268</v>
+        <v>-1.3297</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6077</v>
+        <v>-0.7119</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.8086</v>
+        <v>-1.7891</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2049</v>
+        <v>-0.1283</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.6037</v>
+        <v>-1.6608</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.359</v>
+        <v>-0.9278999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2843</v>
+        <v>0.326</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6433</v>
+        <v>-1.2538</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4496</v>
+        <v>-0.8612</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.4892</v>
+        <v>-0.4542</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.9604</v>
+        <v>-0.407</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3511</v>
+        <v>0.386</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.965</v>
+        <v>-0.386</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3161</v>
+        <v>0.772</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.577</v>
+        <v>-0.6385</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3886</v>
+        <v>-0.0159</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1884</v>
+        <v>-0.6227</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2859</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. LAMBAS VIVANCOS</t>
+          <t>J. SAEZ PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-2.6087</v>
+        <v>-2.1079</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.7898</v>
+        <v>-1.5269</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8189</v>
+        <v>-0.581</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7891</v>
+        <v>-2.8086</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1283</v>
+        <v>-1.2049</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.6608</v>
+        <v>-1.6037</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9278999999999999</v>
+        <v>-0.359</v>
       </c>
       <c r="K5" t="n">
-        <v>0.326</v>
+        <v>0.2843</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2538</v>
+        <v>-0.6433</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8612</v>
+        <v>-2.4496</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4542</v>
+        <v>-1.4892</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.407</v>
+        <v>-0.9604</v>
       </c>
       <c r="P5" t="n">
-        <v>0.386</v>
+        <v>1.3511</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.386</v>
+        <v>-0.965</v>
       </c>
       <c r="R5" t="n">
-        <v>0.772</v>
+        <v>2.3161</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2056</v>
+        <v>-0.6504</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4759</v>
+        <v>-0.4888</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7297</v>
+        <v>-0.1616</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.756</v>
+        <v>-2.757</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3739</v>
+        <v>-0.4553</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.382</v>
+        <v>-2.3017</v>
       </c>
       <c r="G6" t="n">
         <v>-2.6299</v>
@@ -922,13 +922,13 @@
         <v>1.3511</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8679</v>
+        <v>-0.8689</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1507</v>
+        <v>-0.232</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7171999999999999</v>
+        <v>-0.6369</v>
       </c>
       <c r="V6" t="n">
         <v>1.5138</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.1975</v>
+        <v>-3.0845</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.1318</v>
+        <v>-3.0723</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.06569999999999999</v>
+        <v>-0.0122</v>
       </c>
       <c r="G7" t="n">
         <v>-1.9562</v>
@@ -1000,13 +1000,13 @@
         <v>0.386</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6623</v>
+        <v>-0.5493</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1639</v>
+        <v>-0.1044</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4984</v>
+        <v>-0.4449</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8254</v>
+        <v>-3.8868</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5708</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-3.2546</v>
+        <v>-3.3349</v>
       </c>
       <c r="G8" t="n">
         <v>-2.5978</v>
@@ -1078,13 +1078,13 @@
         <v>1.9301</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2928</v>
+        <v>-0.3543</v>
       </c>
       <c r="T8" t="n">
-        <v>0.234</v>
+        <v>0.2529</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5268</v>
+        <v>-0.6071</v>
       </c>
       <c r="V8" t="n">
         <v>-1.5138</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. GUTIERREZ O´CALLAGHAN</t>
+          <t>A. DE CASTRO AYALA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.0962</v>
+        <v>-3.9767</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5562</v>
+        <v>-2.0832</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5399</v>
+        <v>-1.8934</v>
       </c>
       <c r="G9" t="n">
-        <v>-5.3735</v>
+        <v>-2.777</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9448</v>
+        <v>-0.9356</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.4287</v>
+        <v>-1.8414</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.963</v>
+        <v>0.3198</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7092000000000001</v>
+        <v>0.3933</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2538</v>
+        <v>-0.0735</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.4105</v>
+        <v>-3.0968</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2356</v>
+        <v>-1.3288</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.1749</v>
+        <v>-1.7679</v>
       </c>
       <c r="P9" t="n">
-        <v>0.579</v>
+        <v>-0.579</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7371</v>
+        <v>1.3511</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4125</v>
+        <v>-0.6207</v>
       </c>
       <c r="T9" t="n">
-        <v>0.279</v>
+        <v>-0.4729</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1335</v>
+        <v>-0.1477</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2859</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. DE CASTRO AYALA</t>
+          <t>R. SANCHEZ SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2503</v>
+        <v>-4.6796</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.3837</v>
+        <v>-2.2908</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.8667</v>
+        <v>-2.3888</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.777</v>
+        <v>-5.5287</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9356</v>
+        <v>-1.4323</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8414</v>
+        <v>-4.0963</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3198</v>
+        <v>-1.8179</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3933</v>
+        <v>0.1035</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0735</v>
+        <v>-1.9214</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0968</v>
+        <v>-3.7107</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3288</v>
+        <v>-1.5358</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.7679</v>
+        <v>-2.1749</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.579</v>
+        <v>1.5441</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9301</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8943</v>
+        <v>-0.695</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7733</v>
+        <v>-0.4729</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.121</v>
+        <v>-0.2221</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8532</v>
+        <v>-4.76</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.7872</v>
+        <v>-0.5869</v>
       </c>
       <c r="F11" t="n">
-        <v>-4.066</v>
+        <v>-4.1731</v>
       </c>
       <c r="G11" t="n">
         <v>-2.6874</v>
@@ -1312,13 +1312,13 @@
         <v>1.7371</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0959</v>
+        <v>-1.0027</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9518</v>
+        <v>-0.7514999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1441</v>
+        <v>-0.2512</v>
       </c>
       <c r="V11" t="n">
         <v>-1.842</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. SANCHEZ SANCHEZ</t>
+          <t>E. GUTIERREZ O´CALLAGHAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.0871</v>
+        <v>-5.1065</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5913</v>
+        <v>-3.1382</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4959</v>
+        <v>-1.9682</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.5287</v>
+        <v>-5.3735</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.4323</v>
+        <v>-1.9448</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.0963</v>
+        <v>-3.4287</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8179</v>
+        <v>-1.963</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1035</v>
+        <v>-0.7092000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9214</v>
+        <v>-1.2538</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.7107</v>
+        <v>-3.4105</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5358</v>
+        <v>-1.2356</v>
       </c>
       <c r="O12" t="n">
         <v>-2.1749</v>
       </c>
       <c r="P12" t="n">
-        <v>1.5441</v>
+        <v>0.579</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5441</v>
+        <v>1.7371</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1025</v>
+        <v>-0.5979</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7733</v>
+        <v>-0.303</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3292</v>
+        <v>-0.2948</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2859</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.5279</v>
+        <v>-6.522</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.897</v>
+        <v>-6.0784</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6309</v>
+        <v>-0.4435</v>
       </c>
       <c r="G13" t="n">
         <v>-5.9247</v>
@@ -1468,13 +1468,13 @@
         <v>2.3161</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9313</v>
+        <v>-0.9254</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1151</v>
+        <v>-0.0664</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0464</v>
+        <v>-0.859</v>
       </c>
       <c r="V13" t="n">
         <v>0.3281</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-40.3892</v>
+        <v>-39.7944</v>
       </c>
       <c r="E14" t="n">
-        <v>-22.0494</v>
+        <v>-21.4542</v>
       </c>
       <c r="F14" t="n">
-        <v>-18.3397</v>
+        <v>-18.3399</v>
       </c>
       <c r="G14" t="n">
         <v>-38.6519</v>
@@ -1537,7 +1537,7 @@
         <v>-12.274</v>
       </c>
       <c r="P14" t="n">
-        <v>6.755400000000001</v>
+        <v>6.7554</v>
       </c>
       <c r="Q14" t="n">
         <v>-12.5454</v>
@@ -1546,13 +1546,13 @@
         <v>19.301</v>
       </c>
       <c r="S14" t="n">
-        <v>-7.878700000000001</v>
+        <v>-7.2842</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.2913</v>
+        <v>-2.6965</v>
       </c>
       <c r="U14" t="n">
-        <v>-4.587499999999999</v>
+        <v>-4.587400000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-0.6140000000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.7774</v>
+        <v>10.092</v>
       </c>
       <c r="E15" t="n">
-        <v>7.8191</v>
+        <v>7.5187</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9583</v>
+        <v>2.5734</v>
       </c>
       <c r="G15" t="n">
         <v>9.649800000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.9301</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0926</v>
+        <v>1.4072</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1409</v>
+        <v>0.8405</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0483</v>
+        <v>0.5668</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SAINSBURY GARCIA</t>
+          <t>M. KHATIASHVILI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.2253</v>
+        <v>6.2197</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8004</v>
+        <v>2.7646</v>
       </c>
       <c r="F16" t="n">
-        <v>5.425</v>
+        <v>3.4551</v>
       </c>
       <c r="G16" t="n">
-        <v>4.4659</v>
+        <v>11.0858</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0804</v>
+        <v>6.661</v>
       </c>
       <c r="I16" t="n">
-        <v>2.3855</v>
+        <v>4.4248</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8766</v>
+        <v>9.049300000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9405</v>
+        <v>5.9404</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9361</v>
+        <v>3.1089</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5893</v>
+        <v>2.0365</v>
       </c>
       <c r="N16" t="n">
-        <v>0.1399</v>
+        <v>0.7206</v>
       </c>
       <c r="O16" t="n">
-        <v>1.4494</v>
+        <v>1.3159</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.9301</v>
+        <v>-5.7902</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.0532</v>
+        <v>-7.9133</v>
       </c>
       <c r="R16" t="n">
         <v>2.1231</v>
       </c>
       <c r="S16" t="n">
-        <v>3.0755</v>
+        <v>1.5381</v>
       </c>
       <c r="T16" t="n">
-        <v>1.363</v>
+        <v>1.0146</v>
       </c>
       <c r="U16" t="n">
-        <v>1.7126</v>
+        <v>0.5235</v>
       </c>
       <c r="V16" t="n">
-        <v>0.614</v>
+        <v>-0.614</v>
       </c>
       <c r="W16" t="n">
         <v>0.614</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. BOL MEEN</t>
+          <t>U. RUA ALVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.1465</v>
+        <v>6.0231</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.7768</v>
+        <v>2.0045</v>
       </c>
       <c r="F17" t="n">
-        <v>5.9233</v>
+        <v>4.0186</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8981</v>
+        <v>3.8796</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0805</v>
+        <v>1.2142</v>
       </c>
       <c r="I17" t="n">
-        <v>0.8175</v>
+        <v>2.6654</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.0848</v>
+        <v>1.9433</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.58</v>
+        <v>0.6002999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.5048</v>
+        <v>1.3431</v>
       </c>
       <c r="M17" t="n">
-        <v>1.9829</v>
+        <v>1.9363</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6605</v>
+        <v>0.6139</v>
       </c>
       <c r="O17" t="n">
         <v>1.3223</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>1.3511</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.9301</v>
+        <v>-0.193</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9301</v>
+        <v>1.5441</v>
       </c>
       <c r="S17" t="n">
-        <v>4.5343</v>
+        <v>0.4643</v>
       </c>
       <c r="T17" t="n">
-        <v>2.2381</v>
+        <v>0.2542</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2962</v>
+        <v>0.2102</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2859</v>
+        <v>0.3281</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. KHATIASHVILI</t>
+          <t>D. SAINSBURY GARCIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>5.057</v>
+        <v>4.9886</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1638</v>
+        <v>0.0994</v>
       </c>
       <c r="F18" t="n">
-        <v>2.8933</v>
+        <v>4.8893</v>
       </c>
       <c r="G18" t="n">
-        <v>11.0858</v>
+        <v>4.4659</v>
       </c>
       <c r="H18" t="n">
-        <v>6.661</v>
+        <v>2.0804</v>
       </c>
       <c r="I18" t="n">
-        <v>4.4248</v>
+        <v>2.3855</v>
       </c>
       <c r="J18" t="n">
-        <v>9.049300000000001</v>
+        <v>2.8766</v>
       </c>
       <c r="K18" t="n">
-        <v>5.9404</v>
+        <v>1.9405</v>
       </c>
       <c r="L18" t="n">
-        <v>3.1089</v>
+        <v>0.9361</v>
       </c>
       <c r="M18" t="n">
-        <v>2.0365</v>
+        <v>1.5893</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7206</v>
+        <v>0.1399</v>
       </c>
       <c r="O18" t="n">
-        <v>1.3159</v>
+        <v>1.4494</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.7902</v>
+        <v>-1.9301</v>
       </c>
       <c r="Q18" t="n">
-        <v>-7.9133</v>
+        <v>-4.0532</v>
       </c>
       <c r="R18" t="n">
         <v>2.1231</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3754</v>
+        <v>1.8388</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4138</v>
+        <v>0.662</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0384</v>
+        <v>1.1768</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.614</v>
+        <v>0.614</v>
       </c>
       <c r="W18" t="n">
         <v>0.614</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>U. RUA ALVAREZ</t>
+          <t>C. DIALLO TOURE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.5197</v>
+        <v>4.2638</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3035</v>
+        <v>2.4179</v>
       </c>
       <c r="F19" t="n">
-        <v>3.2162</v>
+        <v>1.846</v>
       </c>
       <c r="G19" t="n">
-        <v>3.8796</v>
+        <v>3.8903</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2142</v>
+        <v>2.8121</v>
       </c>
       <c r="I19" t="n">
-        <v>2.6654</v>
+        <v>1.0782</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9433</v>
+        <v>3.3091</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6002999999999999</v>
+        <v>3.1463</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3431</v>
+        <v>0.1628</v>
       </c>
       <c r="M19" t="n">
-        <v>1.9363</v>
+        <v>0.5812</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6139</v>
+        <v>-0.3341</v>
       </c>
       <c r="O19" t="n">
-        <v>1.3223</v>
+        <v>0.9154</v>
       </c>
       <c r="P19" t="n">
-        <v>1.3511</v>
+        <v>-0.193</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.193</v>
+        <v>-1.158</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5441</v>
+        <v>0.965</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.0391</v>
+        <v>0.9369</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4468</v>
+        <v>0.6372</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5923</v>
+        <v>0.2997</v>
       </c>
       <c r="V19" t="n">
-        <v>0.3281</v>
+        <v>-0.3704</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3704</v>
       </c>
       <c r="X19" t="n">
-        <v>0.3281</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. DIALLO TOURE</t>
+          <t>J. BOL MEEN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>4.1035</v>
+        <v>3.1342</v>
       </c>
       <c r="E20" t="n">
-        <v>2.4179</v>
+        <v>-1.8783</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6857</v>
+        <v>5.0125</v>
       </c>
       <c r="G20" t="n">
-        <v>3.8903</v>
+        <v>0.8981</v>
       </c>
       <c r="H20" t="n">
-        <v>2.8121</v>
+        <v>0.0805</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0782</v>
+        <v>0.8175</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3091</v>
+        <v>-1.0848</v>
       </c>
       <c r="K20" t="n">
-        <v>3.1463</v>
+        <v>-0.58</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1628</v>
+        <v>-0.5048</v>
       </c>
       <c r="M20" t="n">
-        <v>0.5812</v>
+        <v>1.9829</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3341</v>
+        <v>0.6605</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9154</v>
+        <v>1.3223</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.193</v>
+        <v>-0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.158</v>
+        <v>-1.9301</v>
       </c>
       <c r="R20" t="n">
-        <v>0.965</v>
+        <v>1.9301</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7766</v>
+        <v>2.522</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6372</v>
+        <v>1.1366</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1394</v>
+        <v>1.3854</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3704</v>
+        <v>-0.2859</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3704</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-0.2859</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
+          <t>A. PEREZ PEREZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.4266</v>
+        <v>2.681</v>
       </c>
       <c r="E21" t="n">
-        <v>2.144</v>
+        <v>0.7366</v>
       </c>
       <c r="F21" t="n">
-        <v>0.2827</v>
+        <v>1.9444</v>
       </c>
       <c r="G21" t="n">
-        <v>0.8682</v>
+        <v>1.4782</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7411</v>
+        <v>1.0598</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1271</v>
+        <v>0.4184</v>
       </c>
       <c r="J21" t="n">
-        <v>1.035</v>
+        <v>0.3966</v>
       </c>
       <c r="K21" t="n">
-        <v>1.035</v>
+        <v>0.3724</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.0243</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1668</v>
+        <v>1.0815</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2939</v>
+        <v>0.6874</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1271</v>
+        <v>0.3941</v>
       </c>
       <c r="P21" t="n">
-        <v>0.193</v>
+        <v>-0.386</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1.158</v>
       </c>
       <c r="R21" t="n">
-        <v>0.193</v>
+        <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1375</v>
+        <v>0.075</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.119</v>
+        <v>-0.0159</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2564</v>
+        <v>0.09089999999999999</v>
       </c>
       <c r="V21" t="n">
-        <v>1.228</v>
+        <v>1.5138</v>
       </c>
       <c r="W21" t="n">
-        <v>1.228</v>
+        <v>1.5138</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. PEREZ PEREZ</t>
+          <t>E. MIGUEL PEREZ DEL NOTARIO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,64 +2125,64 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.906</v>
+        <v>2.5198</v>
       </c>
       <c r="E22" t="n">
-        <v>0.336</v>
+        <v>2.3442</v>
       </c>
       <c r="F22" t="n">
-        <v>1.57</v>
+        <v>0.1756</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4782</v>
+        <v>0.8682</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0598</v>
+        <v>0.7411</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4184</v>
+        <v>0.1271</v>
       </c>
       <c r="J22" t="n">
-        <v>0.3966</v>
+        <v>1.035</v>
       </c>
       <c r="K22" t="n">
-        <v>0.3724</v>
+        <v>1.035</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0243</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0815</v>
+        <v>-0.1668</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6874</v>
+        <v>-0.2939</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3941</v>
+        <v>0.1271</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.386</v>
+        <v>0.193</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.158</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.772</v>
+        <v>0.193</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.7</v>
+        <v>0.2307</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4164</v>
+        <v>0.0813</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2836</v>
+        <v>0.1494</v>
       </c>
       <c r="V22" t="n">
-        <v>1.5138</v>
+        <v>1.228</v>
       </c>
       <c r="W22" t="n">
-        <v>1.5138</v>
+        <v>1.228</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1.2271</v>
+        <v>1.8022</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1321</v>
+        <v>2.3324</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.905</v>
+        <v>-0.5302</v>
       </c>
       <c r="G23" t="n">
         <v>2.4359</v>
@@ -2248,13 +2248,13 @@
         <v>0.965</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3741</v>
+        <v>0.2009</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2234</v>
+        <v>-0.0231</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1507</v>
+        <v>0.2241</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7997</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>40.38910000000001</v>
+        <v>41.7244</v>
       </c>
       <c r="E24" t="n">
         <v>18.34</v>
       </c>
       <c r="F24" t="n">
-        <v>22.0495</v>
+        <v>23.3847</v>
       </c>
       <c r="G24" t="n">
         <v>38.65180000000001</v>
@@ -2317,7 +2317,7 @@
         <v>9.2178</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.7552</v>
+        <v>-6.755199999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>-19.3007</v>
@@ -2326,13 +2326,13 @@
         <v>12.5455</v>
       </c>
       <c r="S24" t="n">
-        <v>7.8787</v>
+        <v>9.213900000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>4.587400000000001</v>
+        <v>4.5874</v>
       </c>
       <c r="U24" t="n">
-        <v>3.291299999999999</v>
+        <v>4.6268</v>
       </c>
       <c r="V24" t="n">
         <v>0.6139000000000001</v>
@@ -2341,7 +2341,7 @@
         <v>4.7851</v>
       </c>
       <c r="X24" t="n">
-        <v>-4.171200000000001</v>
+        <v>-4.1712</v>
       </c>
     </row>
   </sheetData>
